--- a/data/trans_orig/IP31KM01_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM01_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>69450</t>
+          <t>57210</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>66167</t>
+          <t>52869</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70904</t>
+          <t>59560</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>71410</t>
+          <t>53073</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>67317</t>
+          <t>49904</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73544</t>
+          <t>54413</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>140861</t>
+          <t>110284</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>135514</t>
+          <t>104984</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>143892</t>
+          <t>112890</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3053</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>703</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7394</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5,07%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>12,27%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1950</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5233</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7,33%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>1849</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>509</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7290</t>
+          <t>5018</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>5146</t>
+          <t>4902</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2115</t>
+          <t>2296</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10493</t>
+          <t>10202</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>91695</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>83627</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>99469</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>79,77%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>72,75%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>86,53%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>107979</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>98978</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>118073</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>85,94%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>78,77%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>93,97%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>101080</t>
+          <t>81678</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>91745</t>
+          <t>74541</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108523</t>
+          <t>87502</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>209058</t>
+          <t>173374</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>196351</t>
+          <t>162734</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>222126</t>
+          <t>183198</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>85,49%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>23256</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>15482</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>31324</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>20,23%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>13,47%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>27,25%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>17670</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7576</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>26671</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>14,06%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>21,23%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>25343</t>
+          <t>17655</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17900</t>
+          <t>11831</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>34678</t>
+          <t>24792</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>43013</t>
+          <t>40910</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29945</t>
+          <t>31086</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>55720</t>
+          <t>51550</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>53032</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>49138</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>55327</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>92,55%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>85,76%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>96,56%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>50591</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>46182</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>53170</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>91,07%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>83,13%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>95,71%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>59576</t>
+          <t>49234</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55012</t>
+          <t>44413</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62339</t>
+          <t>51713</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>110167</t>
+          <t>102266</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>103923</t>
+          <t>96688</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>114191</t>
+          <t>106089</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,22%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4961</t>
+          <t>4267</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9370</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5057</t>
+          <t>4878</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2294</t>
+          <t>2399</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9621</t>
+          <t>9699</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>10018</t>
+          <t>9145</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16262</t>
+          <t>14723</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>56255</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>46394</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>62705</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>80,58%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>66,45%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>89,81%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>63441</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>57816</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>66836</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>91,04%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>82,97%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>95,92%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>61567</t>
+          <t>64840</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52362</t>
+          <t>59717</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68769</t>
+          <t>67980</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>125009</t>
+          <t>121095</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>114673</t>
+          <t>110373</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>132768</t>
+          <t>128497</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,6%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13561</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7111</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>23422</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>19,42%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>10,19%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>33,55%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>6241</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2846</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>11866</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>8,96%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4,08%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>17,03%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>13800</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6598</t>
+          <t>2482</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23005</t>
+          <t>10745</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>20040</t>
+          <t>19183</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12281</t>
+          <t>11781</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>30376</t>
+          <t>29905</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,74 +2092,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>33647</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>31381</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>98,38%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>34818</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>32456</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>35370</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>98,44%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>91,76%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>40719</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>137</t>
@@ -2167,17 +2167,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>74366</t>
+          <t>74397</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>72058</t>
+          <t>72113</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2205,107 +2205,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>553</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>552</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2819</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2914</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>8,24%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>552</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>2836</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>553</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>2861</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>45681</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>42374</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>46906</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>96,76%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>89,76%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>37798</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>33354</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>40773</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>85,34%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>75,31%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>92,06%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>52015</t>
+          <t>37605</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48811</t>
+          <t>33085</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53342</t>
+          <t>40718</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>89813</t>
+          <t>83286</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>84787</t>
+          <t>78002</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>93393</t>
+          <t>86649</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>94,7%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1528</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4835</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>10,24%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>6492</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>3517</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>10936</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>14,66%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>7,94%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>24,69%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>6681</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>3568</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4971</t>
+          <t>11201</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>8259</t>
+          <t>8209</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>4846</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13285</t>
+          <t>13493</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>116978</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>108104</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>124827</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>83,22%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>76,9%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>88,8%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>105673</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>97705</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>111374</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>85,43%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>78,99%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>90,04%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>126799</t>
+          <t>103035</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>110307</t>
+          <t>95710</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>136826</t>
+          <t>109453</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>232472</t>
+          <t>220014</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>212944</t>
+          <t>208046</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>243374</t>
+          <t>230648</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,9%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>23593</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>15744</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>32467</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>16,78%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>11,2%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>23,1%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>18023</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>12322</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>25991</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>14,57%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>9,96%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>21,01%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>28245</t>
+          <t>18787</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>18218</t>
+          <t>12369</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>44737</t>
+          <t>26112</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>46268</t>
+          <t>42380</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>35366</t>
+          <t>31746</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>65796</t>
+          <t>54348</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>20,71%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,74 +3121,74 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>127271</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>124063</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>98,92%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>96,42%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>136487</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>133058</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>137900</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>98,98%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>96,49%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>154159</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>384</t>
@@ -3196,27 +3196,27 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>281429</t>
+          <t>293623</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>278126</t>
+          <t>289650</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3234,107 +3234,107 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>1394</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>1413</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>4602</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>4842</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>3,51%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1413</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>5386</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1394</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>4697</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>853</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>617565</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>601064</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>631556</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>89,92%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>87,51%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>91,95%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>831</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>595849</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>580984</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>606819</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>91,23%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>88,95%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>92,91%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>853</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>667324</t>
+          <t>560772</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>646433</t>
+          <t>547624</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>682126</t>
+          <t>572223</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1263174</t>
+          <t>1178336</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1238024</t>
+          <t>1159390</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1281985</t>
+          <t>1197619</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,77%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>69259</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>55268</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>85760</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>10,08%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>8,05%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>12,49%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>57285</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>46315</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>72150</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>8,77%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>7,09%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>11,05%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>77409</t>
+          <t>57436</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>62607</t>
+          <t>45985</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>98300</t>
+          <t>70584</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>134693</t>
+          <t>126695</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>115882</t>
+          <t>107412</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>159843</t>
+          <t>145641</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
